--- a/public/downloads/BackSingle2018.xlsx
+++ b/public/downloads/BackSingle2018.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,13 +169,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>O</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>HO</t>
   </si>
   <si>
     <t>HO2</t>
+  </si>
+  <si>
+    <t>O</t>
   </si>
 </sst>
 </file>
@@ -659,10 +682,10 @@
         <v>141</v>
       </c>
       <c r="N3" s="5">
-        <v>1534.149020195007</v>
+        <v>1534149.020195007</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03247701046181056</v>
+        <v>32.47701046181056</v>
       </c>
       <c r="P3" s="5">
         <v>47238</v>
@@ -709,10 +732,10 @@
         <v>141</v>
       </c>
       <c r="N4" s="5">
-        <v>816.0615184307098</v>
+        <v>816061.5184307098</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04288965777215062</v>
+        <v>42.88965777215062</v>
       </c>
       <c r="P4" s="5">
         <v>19027</v>
@@ -759,10 +782,10 @@
         <v>141</v>
       </c>
       <c r="N5" s="5">
-        <v>2241.1381046772</v>
+        <v>2241138.1046772</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1324314899649708</v>
+        <v>132.4314899649708</v>
       </c>
       <c r="P5" s="5">
         <v>16923</v>
@@ -809,10 +832,10 @@
         <v>141</v>
       </c>
       <c r="N6" s="5">
-        <v>1585.935954093933</v>
+        <v>1585935.954093933</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08393860241843618</v>
+        <v>83.93860241843618</v>
       </c>
       <c r="P6" s="5">
         <v>18894</v>
@@ -859,10 +882,10 @@
         <v>141</v>
       </c>
       <c r="N7" s="5">
-        <v>2241.863418340683</v>
+        <v>2241863.418340683</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1507540460184711</v>
+        <v>150.7540460184711</v>
       </c>
       <c r="P7" s="5">
         <v>14871</v>
@@ -909,10 +932,10 @@
         <v>141</v>
       </c>
       <c r="N8" s="5">
-        <v>175.010101556778</v>
+        <v>175010.101556778</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01211058761032302</v>
+        <v>12.11058761032302</v>
       </c>
       <c r="P8" s="5">
         <v>14451</v>
@@ -959,10 +982,10 @@
         <v>141</v>
       </c>
       <c r="N9" s="5">
-        <v>729.8953635692596</v>
+        <v>729895.3635692596</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03015348936500288</v>
+        <v>30.15348936500288</v>
       </c>
       <c r="P9" s="5">
         <v>24206</v>
@@ -1009,10 +1032,10 @@
         <v>141</v>
       </c>
       <c r="N10" s="5">
-        <v>1918.966547489166</v>
+        <v>1918966.547489166</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08695303581898438</v>
+        <v>86.95303581898438</v>
       </c>
       <c r="P10" s="5">
         <v>22069</v>
@@ -1059,10 +1082,10 @@
         <v>141</v>
       </c>
       <c r="N11" s="5">
-        <v>645.4365818500519</v>
+        <v>645436.5818500519</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03967034922249858</v>
+        <v>39.67034922249857</v>
       </c>
       <c r="P11" s="5">
         <v>16270</v>
@@ -1109,10 +1132,10 @@
         <v>141</v>
       </c>
       <c r="N12" s="5">
-        <v>318.3620235919952</v>
+        <v>318362.0235919952</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01881461045990162</v>
+        <v>18.81461045990162</v>
       </c>
       <c r="P12" s="5">
         <v>16921</v>
@@ -1159,10 +1182,10 @@
         <v>141</v>
       </c>
       <c r="N13" s="5">
-        <v>2068.275821208954</v>
+        <v>2068275.821208954</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07859683911111358</v>
+        <v>78.59683911111358</v>
       </c>
       <c r="P13" s="5">
         <v>26315</v>
@@ -1209,10 +1232,10 @@
         <v>141</v>
       </c>
       <c r="N14" s="5">
-        <v>1727.644520521164</v>
+        <v>1727644.520521164</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2186061648135093</v>
+        <v>218.6061648135093</v>
       </c>
       <c r="P14" s="5">
         <v>7903</v>
@@ -1259,10 +1282,10 @@
         <v>141</v>
       </c>
       <c r="N15" s="5">
-        <v>2954.267071008682</v>
+        <v>2954267.071008682</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2049155213295888</v>
+        <v>204.9155213295888</v>
       </c>
       <c r="P15" s="5">
         <v>14417</v>
@@ -1309,10 +1332,10 @@
         <v>141</v>
       </c>
       <c r="N16" s="5">
-        <v>1329.634772777557</v>
+        <v>1329634.772777557</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09792567187933107</v>
+        <v>97.92567187933108</v>
       </c>
       <c r="P16" s="5">
         <v>13578</v>
@@ -1359,10 +1382,10 @@
         <v>141</v>
       </c>
       <c r="N17" s="5">
-        <v>1819.041528701782</v>
+        <v>1819041.528701782</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1001950718095171</v>
+        <v>100.1950718095171</v>
       </c>
       <c r="P17" s="5">
         <v>18155</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,34 +1497,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4728725588503895</v>
+        <v>0.8767570532616891</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3974466122568988</v>
+        <v>0.6067724178983758</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3873958356936334</v>
+        <v>0.9233687322290283</v>
       </c>
       <c r="E3" s="4">
-        <v>86.33521493703863</v>
+        <v>75.87494572297007</v>
       </c>
       <c r="F3" s="4">
-        <v>86.97058403541241</v>
+        <v>81.6164500928182</v>
       </c>
       <c r="G3" s="5">
         <v>47</v>
       </c>
       <c r="H3" s="5">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J3" s="5">
         <v>9</v>
@@ -1496,96 +1551,150 @@
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>5</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.7748966852712592</v>
+      </c>
+      <c r="O3" s="5">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7634253370149643</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6664614034207113</v>
+      </c>
+      <c r="R3" s="5">
+        <v>35</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3037413108765422</v>
+        <v>1.194847695675462</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2621194151328299</v>
+        <v>0.530617475163084</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2595745616348023</v>
+        <v>1.384450816784594</v>
       </c>
       <c r="E4" s="4">
-        <v>83.62353452019103</v>
+        <v>62.46200607902752</v>
       </c>
       <c r="F4" s="4">
-        <v>80.9055642819737</v>
+        <v>72.41896330144269</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I4" s="5">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J4" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.6444260867928325</v>
+      </c>
+      <c r="O4" s="5">
+        <v>27</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9184640568242065</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4547181116203126</v>
+      </c>
+      <c r="R4" s="5">
+        <v>26</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4554312172653363</v>
+        <v>1.30525729542627</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3696707897026265</v>
+        <v>0.8339825978105095</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3603372827339337</v>
+        <v>1.386310769283565</v>
       </c>
       <c r="E5" s="4">
-        <v>83.12201476335214</v>
+        <v>87.69214068606145</v>
       </c>
       <c r="F5" s="4">
-        <v>80.1335142081963</v>
+        <v>91.406778047503</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I5" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.101166942049926</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.9625656055913369</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6070942746090356</v>
+      </c>
+      <c r="R5" s="5">
+        <v>38</v>
+      </c>
+      <c r="S5" s="5">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,132 +1797,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.500039213065743</v>
+        <v>0.8110501244456944</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5431992768347506</v>
+        <v>0.7121386575232733</v>
       </c>
       <c r="D3" s="4">
-        <v>1.558367151713723</v>
+        <v>0.8762548210642443</v>
       </c>
       <c r="E3" s="4">
-        <v>83.65971920683177</v>
+        <v>59.58242871616751</v>
       </c>
       <c r="F3" s="4">
-        <v>91.12094816507175</v>
+        <v>72.21143319529706</v>
       </c>
       <c r="G3" s="5">
         <v>47</v>
       </c>
       <c r="H3" s="5">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J3" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
         <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.6089381792141837</v>
+      </c>
+      <c r="O3" s="5">
+        <v>27</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7034575813367234</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5503931943900676</v>
+      </c>
+      <c r="R3" s="5">
+        <v>27</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.316956155569197</v>
+        <v>1.585551136820617</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4714201980880346</v>
+        <v>0.9067214583845384</v>
       </c>
       <c r="D4" s="4">
-        <v>1.451529761202359</v>
+        <v>1.339848148825366</v>
       </c>
       <c r="E4" s="4">
-        <v>66.51396728904324</v>
+        <v>51.56028368794322</v>
       </c>
       <c r="F4" s="4">
-        <v>77.87162644580829</v>
+        <v>67.82378980436894</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I4" s="5">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J4" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L4" s="5">
         <v>7</v>
       </c>
       <c r="M4" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.131688956146478</v>
+      </c>
+      <c r="O4" s="5">
+        <v>19</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.344216851012695</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5993366754222095</v>
+      </c>
+      <c r="R4" s="5">
+        <v>19</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.517908133462871</v>
+        <v>1.435427330618969</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5828440106016236</v>
+        <v>0.9175416369784476</v>
       </c>
       <c r="D5" s="4">
-        <v>1.68142729884368</v>
+        <v>1.407736242434537</v>
       </c>
       <c r="E5" s="4">
-        <v>64.56288898538125</v>
+        <v>78.51715154146812</v>
       </c>
       <c r="F5" s="4">
-        <v>77.19501166166748</v>
+        <v>87.40539768670317</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I5" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M5" s="5">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.143271876687179</v>
+      </c>
+      <c r="O5" s="5">
+        <v>38</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.136192441521072</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8608720656298248</v>
+      </c>
+      <c r="R5" s="5">
+        <v>37</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,132 +2097,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.063251082064488</v>
+        <v>0.3037413108765422</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5403363648653573</v>
+        <v>0.2621194151328299</v>
       </c>
       <c r="D3" s="4">
-        <v>1.114895173952933</v>
+        <v>0.2595745616348023</v>
       </c>
       <c r="E3" s="4">
-        <v>84.78506296135451</v>
+        <v>83.62353452019103</v>
       </c>
       <c r="F3" s="4">
-        <v>91.86134513779749</v>
+        <v>80.9055642819737</v>
       </c>
       <c r="G3" s="5">
         <v>47</v>
       </c>
       <c r="H3" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.0344012044379975</v>
+      </c>
+      <c r="O3" s="5">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3012591198822419</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2598343659024376</v>
+      </c>
+      <c r="R3" s="5">
+        <v>36</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6979922514453218</v>
+        <v>0.4554312172653363</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4685505993043989</v>
+        <v>0.3696707897026265</v>
       </c>
       <c r="D4" s="4">
-        <v>0.766605247203246</v>
+        <v>0.3603372827339337</v>
       </c>
       <c r="E4" s="4">
-        <v>75.38717614705449</v>
+        <v>83.12201476335214</v>
       </c>
       <c r="F4" s="4">
-        <v>85.2341853491337</v>
+        <v>80.1335142081963</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.2756294876654406</v>
+      </c>
+      <c r="O4" s="5">
+        <v>33</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3878119325239524</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2519578915093679</v>
+      </c>
+      <c r="R4" s="5">
+        <v>33</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.107622271154566</v>
+        <v>0.4728725588503895</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2805606136224496</v>
+        <v>0.3974466122568988</v>
       </c>
       <c r="D5" s="4">
-        <v>1.185932105985344</v>
+        <v>0.3873958356936334</v>
       </c>
       <c r="E5" s="4">
-        <v>74.94861774497038</v>
+        <v>86.33521493703863</v>
       </c>
       <c r="F5" s="4">
-        <v>84.43167214051014</v>
+        <v>86.97058403541241</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I5" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M5" s="5">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.1192052031840599</v>
+      </c>
+      <c r="O5" s="5">
+        <v>38</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4483427234616537</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3827919741687333</v>
+      </c>
+      <c r="R5" s="5">
+        <v>38</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,119 +2397,173 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.436068798771536</v>
+        <v>1.316956155569197</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5257451427488055</v>
+        <v>0.4714201980880346</v>
       </c>
       <c r="D3" s="4">
-        <v>1.423531608415439</v>
+        <v>1.451529761202359</v>
       </c>
       <c r="E3" s="4">
-        <v>80.73382544507122</v>
+        <v>66.51396728904324</v>
       </c>
       <c r="F3" s="4">
-        <v>90.23704126802593</v>
+        <v>77.87162644580829</v>
       </c>
       <c r="G3" s="5">
         <v>47</v>
       </c>
       <c r="H3" s="5">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J3" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>7</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.018359458825591</v>
+      </c>
+      <c r="O3" s="5">
+        <v>34</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.196703691354235</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.740438088329608</v>
+      </c>
+      <c r="R3" s="5">
+        <v>29</v>
+      </c>
+      <c r="S3" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.9391663970793664</v>
+        <v>1.517908133462871</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3463416710102606</v>
+        <v>0.5828440106016236</v>
       </c>
       <c r="D4" s="4">
-        <v>0.9774820928942256</v>
+        <v>1.68142729884368</v>
       </c>
       <c r="E4" s="4">
-        <v>70.07236937328121</v>
+        <v>64.56288898538125</v>
       </c>
       <c r="F4" s="4">
-        <v>82.68813365700402</v>
+        <v>77.19501166166748</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>11</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.554395866813762</v>
+      </c>
+      <c r="O4" s="5">
+        <v>35</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.359926096817366</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.08453935948311</v>
+      </c>
+      <c r="R4" s="5">
+        <v>29</v>
+      </c>
+      <c r="S4" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.146341734007462</v>
+        <v>1.500039213065743</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4638971582509157</v>
+        <v>0.5431992768347506</v>
       </c>
       <c r="D5" s="4">
-        <v>1.389890430097539</v>
+        <v>1.558367151713723</v>
       </c>
       <c r="E5" s="4">
-        <v>56.86857721812126</v>
+        <v>83.65971920683177</v>
       </c>
       <c r="F5" s="4">
-        <v>71.46413441858265</v>
+        <v>91.12094816507175</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I5" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
@@ -2220,11 +2572,29 @@
         <v>3</v>
       </c>
       <c r="M5" s="5">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.305764966586477</v>
+      </c>
+      <c r="O5" s="5">
+        <v>43</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.301237501700734</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.9342369089634123</v>
+      </c>
+      <c r="R5" s="5">
+        <v>35</v>
+      </c>
+      <c r="S5" s="5">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2697,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3971037654584805</v>
+        <v>0.6979922514453218</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3655771819047194</v>
+        <v>0.4685505993043989</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3575376885382105</v>
+        <v>0.766605247203246</v>
       </c>
       <c r="E3" s="4">
-        <v>94.31610942249233</v>
+        <v>75.38717614705449</v>
       </c>
       <c r="F3" s="4">
-        <v>95.61759246037396</v>
+        <v>85.2341853491337</v>
       </c>
       <c r="G3" s="5">
         <v>47</v>
       </c>
       <c r="H3" s="5">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
         <v>2</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.5647150715965751</v>
+      </c>
+      <c r="O3" s="5">
+        <v>43</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7023588000728936</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5002360472362449</v>
+      </c>
+      <c r="R3" s="5">
+        <v>40</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2059775933826238</v>
+        <v>1.107622271154566</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2060974941552767</v>
+        <v>0.2805606136224496</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2103815380445552</v>
+        <v>1.185932105985344</v>
       </c>
       <c r="E4" s="4">
-        <v>91.96627587205028</v>
+        <v>74.94861774497038</v>
       </c>
       <c r="F4" s="4">
-        <v>93.32881146175349</v>
+        <v>84.43167214051014</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>6</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.6996515413550923</v>
+      </c>
+      <c r="O4" s="5">
+        <v>40</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.118970351739674</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5637614908317532</v>
+      </c>
+      <c r="R4" s="5">
+        <v>34</v>
+      </c>
+      <c r="S4" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3645787859336788</v>
+        <v>1.063251082064488</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2720807133358347</v>
+        <v>0.5403363648653573</v>
       </c>
       <c r="D5" s="4">
-        <v>0.275501707230189</v>
+        <v>1.114895173952933</v>
       </c>
       <c r="E5" s="4">
-        <v>91.18830510927759</v>
+        <v>84.78506296135451</v>
       </c>
       <c r="F5" s="4">
-        <v>93.53205768955948</v>
+        <v>91.86134513779749</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I5" s="5">
         <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.8374977027656108</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.947426330011351</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6483488076429611</v>
+      </c>
+      <c r="R5" s="5">
+        <v>40</v>
+      </c>
+      <c r="S5" s="5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,132 +2997,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3450511769481974</v>
+        <v>0.9391663970793664</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3067744255028363</v>
+        <v>0.3463416710102606</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2727895109036692</v>
+        <v>0.9774820928942256</v>
       </c>
       <c r="E3" s="4">
-        <v>92.1182515559411</v>
+        <v>70.07236937328121</v>
       </c>
       <c r="F3" s="4">
-        <v>95.13851206625711</v>
+        <v>82.68813365700402</v>
       </c>
       <c r="G3" s="5">
         <v>47</v>
       </c>
       <c r="H3" s="5">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K3" s="5">
         <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>9</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.7542748793563251</v>
+      </c>
+      <c r="O3" s="5">
+        <v>42</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9565939324084106</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7734238647298937</v>
+      </c>
+      <c r="R3" s="5">
+        <v>38</v>
+      </c>
+      <c r="S3" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3743419206811692</v>
+        <v>1.146341734007462</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3607982680510546</v>
+        <v>0.4638971582509157</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3355597110702155</v>
+        <v>1.389890430097539</v>
       </c>
       <c r="E4" s="4">
-        <v>89.28354320451561</v>
+        <v>56.86857721812126</v>
       </c>
       <c r="F4" s="4">
-        <v>92.55937931362702</v>
+        <v>71.46413441858265</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J4" s="5">
+        <v>8</v>
+      </c>
+      <c r="K4" s="5">
         <v>1</v>
       </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.8345364788141784</v>
+      </c>
+      <c r="O4" s="5">
+        <v>28</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.969444158851851</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5742036787370358</v>
+      </c>
+      <c r="R4" s="5">
+        <v>25</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6095873594381106</v>
+        <v>1.436068798771536</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4570303271012865</v>
+        <v>0.5257451427488055</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5550936059660339</v>
+        <v>1.423531608415439</v>
       </c>
       <c r="E5" s="4">
-        <v>80.97481545809782</v>
+        <v>80.73382544507122</v>
       </c>
       <c r="F5" s="4">
-        <v>86.04264838878429</v>
+        <v>90.23704126802593</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I5" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.318331698618082</v>
+      </c>
+      <c r="O5" s="5">
+        <v>45</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.382142275626529</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.030834157306298</v>
+      </c>
+      <c r="R5" s="5">
+        <v>37</v>
+      </c>
+      <c r="S5" s="5">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,25 +3297,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4093027873877129</v>
+        <v>0.2059775933826238</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3771978298346091</v>
+        <v>0.2060974941552767</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3688247409548445</v>
+        <v>0.2103815380445552</v>
       </c>
       <c r="E3" s="4">
-        <v>92.98813142278158</v>
+        <v>91.96627587205028</v>
       </c>
       <c r="F3" s="4">
-        <v>94.78295016421278</v>
+        <v>93.32881146175349</v>
       </c>
       <c r="G3" s="5">
         <v>47</v>
@@ -2771,99 +3348,153 @@
         <v>2</v>
       </c>
       <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
         <v>2</v>
       </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.02467566288585983</v>
+      </c>
+      <c r="O3" s="5">
+        <v>45</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2001170112105181</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1999764416644108</v>
+      </c>
+      <c r="R3" s="5">
+        <v>45</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.274910728218669</v>
+        <v>0.3645787859336788</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2755403381955052</v>
+        <v>0.2720807133358347</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2833518673105038</v>
+        <v>0.275501707230189</v>
       </c>
       <c r="E4" s="4">
-        <v>89.51584889274845</v>
+        <v>91.18830510927759</v>
       </c>
       <c r="F4" s="4">
-        <v>92.4684658955677</v>
+        <v>93.53205768955948</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>1</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1442828888631373</v>
+      </c>
+      <c r="O4" s="5">
+        <v>45</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3249220802192047</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2242489145290223</v>
+      </c>
+      <c r="R4" s="5">
+        <v>45</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3926439898673987</v>
+        <v>0.3971037654584805</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3694566475631929</v>
+        <v>0.3655771819047194</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3834537135830595</v>
+        <v>0.3575376885382105</v>
       </c>
       <c r="E5" s="4">
-        <v>82.55319148936134</v>
+        <v>94.31610942249233</v>
       </c>
       <c r="F5" s="4">
-        <v>87.91137131705418</v>
+        <v>95.61759246037396</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I5" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.03664009310313499</v>
+      </c>
+      <c r="O5" s="5">
+        <v>45</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3974206789050327</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3659081803933406</v>
+      </c>
+      <c r="R5" s="5">
+        <v>45</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,132 +3597,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.085163757201719</v>
+        <v>0.3743419206811692</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5648179089739602</v>
+        <v>0.3607982680510546</v>
       </c>
       <c r="D3" s="4">
-        <v>1.087002428777309</v>
+        <v>0.3355597110702155</v>
       </c>
       <c r="E3" s="4">
-        <v>87.58431031987223</v>
+        <v>89.28354320451561</v>
       </c>
       <c r="F3" s="4">
-        <v>92.25807987053253</v>
+        <v>92.55937931362702</v>
       </c>
       <c r="G3" s="5">
         <v>47</v>
       </c>
       <c r="H3" s="5">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
         <v>1</v>
       </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
       <c r="M3" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3296848563039373</v>
+      </c>
+      <c r="O3" s="5">
+        <v>46</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2030031497407492</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1929018033141893</v>
+      </c>
+      <c r="R3" s="5">
+        <v>46</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7384461923518031</v>
+        <v>0.6095873594381106</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3610983653128916</v>
+        <v>0.4570303271012865</v>
       </c>
       <c r="D4" s="4">
-        <v>0.9377878490316046</v>
+        <v>0.5550936059660339</v>
       </c>
       <c r="E4" s="4">
-        <v>80.52250687509036</v>
+        <v>80.97481545809782</v>
       </c>
       <c r="F4" s="4">
-        <v>85.26845637583871</v>
+        <v>86.04264838878429</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I4" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3075072341801846</v>
+      </c>
+      <c r="O4" s="5">
+        <v>39</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4736065224528891</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3099326541151642</v>
+      </c>
+      <c r="R4" s="5">
+        <v>39</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.086299783753595</v>
+        <v>0.3450511769481974</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2939558220221257</v>
+        <v>0.3067744255028363</v>
       </c>
       <c r="D5" s="4">
-        <v>1.181911453172373</v>
+        <v>0.2727895109036692</v>
       </c>
       <c r="E5" s="4">
-        <v>78.55116514690992</v>
+        <v>92.1182515559411</v>
       </c>
       <c r="F5" s="4">
-        <v>84.90170879147094</v>
+        <v>95.13851206625711</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I5" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.2238735119170081</v>
+      </c>
+      <c r="O5" s="5">
+        <v>46</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.304976290356209</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2706951612005223</v>
+      </c>
+      <c r="R5" s="5">
+        <v>46</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.274910728218669</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2755403381955052</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2833518673105038</v>
+      </c>
+      <c r="E3" s="4">
+        <v>89.51584889274845</v>
+      </c>
+      <c r="F3" s="4">
+        <v>92.4684658955677</v>
+      </c>
+      <c r="G3" s="5">
+        <v>47</v>
+      </c>
+      <c r="H3" s="5">
+        <v>46</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.1503805259377247</v>
+      </c>
+      <c r="O3" s="5">
+        <v>46</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2389093517219295</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2420254649474827</v>
+      </c>
+      <c r="R3" s="5">
+        <v>46</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3926439898673987</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3694566475631929</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3834537135830595</v>
+      </c>
+      <c r="E4" s="4">
+        <v>82.55319148936134</v>
+      </c>
+      <c r="F4" s="4">
+        <v>87.91137131705418</v>
+      </c>
+      <c r="G4" s="5">
+        <v>47</v>
+      </c>
+      <c r="H4" s="5">
+        <v>42</v>
+      </c>
+      <c r="I4" s="5">
+        <v>5</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.3100026498426822</v>
+      </c>
+      <c r="O4" s="5">
+        <v>42</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2844680906301786</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2455546012717974</v>
+      </c>
+      <c r="R4" s="5">
+        <v>42</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4093027873877129</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3771978298346091</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3688247409548445</v>
+      </c>
+      <c r="E5" s="4">
+        <v>92.98813142278158</v>
+      </c>
+      <c r="F5" s="4">
+        <v>94.78295016421278</v>
+      </c>
+      <c r="G5" s="5">
+        <v>47</v>
+      </c>
+      <c r="H5" s="5">
+        <v>45</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.06964174380740845</v>
+      </c>
+      <c r="O5" s="5">
+        <v>45</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4017429298119676</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3693019785888308</v>
+      </c>
+      <c r="R5" s="5">
+        <v>45</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7384461923518031</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3610983653128916</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.9377878490316046</v>
+      </c>
+      <c r="E3" s="4">
+        <v>80.52250687509036</v>
+      </c>
+      <c r="F3" s="4">
+        <v>85.26845637583871</v>
+      </c>
+      <c r="G3" s="5">
+        <v>47</v>
+      </c>
+      <c r="H3" s="5">
+        <v>34</v>
+      </c>
+      <c r="I3" s="5">
+        <v>8</v>
+      </c>
+      <c r="J3" s="5">
+        <v>5</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>5</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.233830676355712</v>
+      </c>
+      <c r="O3" s="5">
+        <v>39</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7982550871973439</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5331812138530291</v>
+      </c>
+      <c r="R3" s="5">
+        <v>34</v>
+      </c>
+      <c r="S3" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.086299783753595</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2939558220221257</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.181911453172373</v>
+      </c>
+      <c r="E4" s="4">
+        <v>78.55116514690992</v>
+      </c>
+      <c r="F4" s="4">
+        <v>84.90170879147094</v>
+      </c>
+      <c r="G4" s="5">
+        <v>47</v>
+      </c>
+      <c r="H4" s="5">
+        <v>28</v>
+      </c>
+      <c r="I4" s="5">
+        <v>6</v>
+      </c>
+      <c r="J4" s="5">
+        <v>13</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>9</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.7361248575750742</v>
+      </c>
+      <c r="O4" s="5">
+        <v>37</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.349286565760216</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.9421993322352538</v>
+      </c>
+      <c r="R4" s="5">
+        <v>29</v>
+      </c>
+      <c r="S4" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.085163757201719</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.5648179089739602</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.087002428777309</v>
+      </c>
+      <c r="E5" s="4">
+        <v>87.58431031987223</v>
+      </c>
+      <c r="F5" s="4">
+        <v>92.25807987053253</v>
+      </c>
+      <c r="G5" s="5">
+        <v>47</v>
+      </c>
+      <c r="H5" s="5">
+        <v>36</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>11</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>7</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.415863675497418</v>
+      </c>
+      <c r="O5" s="5">
+        <v>43</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.184699111131962</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8429679099000625</v>
+      </c>
+      <c r="R5" s="5">
+        <v>39</v>
+      </c>
+      <c r="S5" s="5">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>50.35460992907801</v>
+      </c>
+      <c r="C3" s="3">
+        <v>20.56737588652482</v>
+      </c>
+      <c r="D3" s="3">
+        <v>29.07801418439716</v>
+      </c>
+      <c r="E3" s="3">
+        <v>6.382978723404255</v>
+      </c>
+      <c r="F3" s="3">
+        <v>17.02127659574468</v>
+      </c>
+      <c r="G3" s="3">
+        <v>5.673758865248227</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1.277610732097999</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.6668798178139308</v>
+      </c>
+      <c r="J3" s="4">
+        <v>1.248243804712031</v>
+      </c>
+      <c r="K3" s="4">
+        <v>58.4568437303999</v>
+      </c>
+      <c r="L3" s="4">
+        <v>72.97324955971301</v>
+      </c>
+      <c r="M3" s="5">
+        <v>141</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1534149.020195007</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.47701046181056</v>
+      </c>
+      <c r="P3" s="5">
+        <v>47238</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>78.01418439716312</v>
+      </c>
+      <c r="C4" s="3">
+        <v>7.801418439716312</v>
+      </c>
+      <c r="D4" s="3">
+        <v>14.18439716312057</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4.25531914893617</v>
+      </c>
+      <c r="F4" s="3">
+        <v>9.219858156028367</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.7092198581560284</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.7042236078602245</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.4901761641845234</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.494723055933136</v>
+      </c>
+      <c r="K4" s="4">
+        <v>63.31451729628017</v>
+      </c>
+      <c r="L4" s="4">
+        <v>79.36717597220245</v>
+      </c>
+      <c r="M4" s="5">
+        <v>141</v>
+      </c>
+      <c r="N4" s="5">
+        <v>816061.5184307098</v>
+      </c>
+      <c r="O4" s="4">
+        <v>42.88965777215062</v>
+      </c>
+      <c r="P4" s="5">
+        <v>19027</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>70.21276595744681</v>
+      </c>
+      <c r="C5" s="3">
+        <v>7.092198581560284</v>
+      </c>
+      <c r="D5" s="3">
+        <v>22.69503546099291</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.127659574468085</v>
+      </c>
+      <c r="F5" s="3">
+        <v>7.092198581560284</v>
+      </c>
+      <c r="G5" s="3">
+        <v>13.47517730496454</v>
+      </c>
+      <c r="H5" s="4">
+        <v>1.254065894436948</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.8467139873397904</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1.17015495180058</v>
+      </c>
+      <c r="K5" s="4">
+        <v>72.70444347951945</v>
+      </c>
+      <c r="L5" s="4">
+        <v>82.84568518254085</v>
+      </c>
+      <c r="M5" s="5">
+        <v>141</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2241138.1046772</v>
+      </c>
+      <c r="O5" s="4">
+        <v>132.4314899649708</v>
+      </c>
+      <c r="P5" s="5">
+        <v>16923</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>68.08510638297872</v>
+      </c>
+      <c r="C6" s="3">
+        <v>10.63829787234043</v>
+      </c>
+      <c r="D6" s="3">
+        <v>21.27659574468085</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2.836879432624114</v>
+      </c>
+      <c r="F6" s="3">
+        <v>14.18439716312057</v>
+      </c>
+      <c r="G6" s="3">
+        <v>4.25531914893617</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.8532498824507394</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.6366419297579938</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.7534536660334271</v>
+      </c>
+      <c r="K6" s="4">
+        <v>68.09547932648229</v>
+      </c>
+      <c r="L6" s="4">
+        <v>79.64070953718166</v>
+      </c>
+      <c r="M6" s="5">
+        <v>141</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1585935.954093933</v>
+      </c>
+      <c r="O6" s="4">
+        <v>83.93860241843618</v>
+      </c>
+      <c r="P6" s="5">
+        <v>18894</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>75.177304964539</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.836879432624114</v>
+      </c>
+      <c r="D7" s="3">
+        <v>21.98581560283688</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1.418439716312057</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2.836879432624114</v>
+      </c>
+      <c r="G7" s="3">
+        <v>17.73049645390071</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1.319201123017655</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.92019239533171</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1.328017371574598</v>
+      </c>
+      <c r="K7" s="4">
+        <v>83.29256525305168</v>
+      </c>
+      <c r="L7" s="4">
+        <v>89.42738826217287</v>
+      </c>
+      <c r="M7" s="5">
+        <v>141</v>
+      </c>
+      <c r="N7" s="5">
+        <v>2241863.418340683</v>
+      </c>
+      <c r="O7" s="4">
+        <v>150.7540460184711</v>
+      </c>
+      <c r="P7" s="5">
+        <v>14871</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>70.21276595744681</v>
+      </c>
+      <c r="C8" s="3">
+        <v>17.73049645390071</v>
+      </c>
+      <c r="D8" s="3">
+        <v>12.05673758865248</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.7092198581560284</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5.673758865248227</v>
+      </c>
+      <c r="G8" s="3">
+        <v>5.673758865248227</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.8814849998101693</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.5880646712827915</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.8888485023750241</v>
+      </c>
+      <c r="K8" s="4">
+        <v>75.34303082935307</v>
+      </c>
+      <c r="L8" s="4">
+        <v>81.81406381392127</v>
+      </c>
+      <c r="M8" s="5">
+        <v>141</v>
+      </c>
+      <c r="N8" s="5">
+        <v>175010.101556778</v>
+      </c>
+      <c r="O8" s="4">
+        <v>12.11058761032302</v>
+      </c>
+      <c r="P8" s="5">
+        <v>14451</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>58.86524822695035</v>
+      </c>
+      <c r="C9" s="3">
+        <v>18.43971631205673</v>
+      </c>
+      <c r="D9" s="3">
+        <v>22.69503546099291</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6.382978723404255</v>
+      </c>
+      <c r="F9" s="3">
+        <v>15.60283687943262</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.7092198581560284</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1.06128895795683</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.7000033675886423</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.7418137560579873</v>
+      </c>
+      <c r="K9" s="4">
+        <v>63.21995464852613</v>
+      </c>
+      <c r="L9" s="4">
+        <v>75.81354022879113</v>
+      </c>
+      <c r="M9" s="5">
+        <v>141</v>
+      </c>
+      <c r="N9" s="5">
+        <v>729895.3635692596</v>
+      </c>
+      <c r="O9" s="4">
+        <v>30.15348936500288</v>
+      </c>
+      <c r="P9" s="5">
+        <v>24206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>75.88652482269504</v>
+      </c>
+      <c r="C10" s="3">
+        <v>7.092198581560284</v>
+      </c>
+      <c r="D10" s="3">
+        <v>17.02127659574468</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.7092198581560284</v>
+      </c>
+      <c r="F10" s="3">
+        <v>16.31205673758866</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.3791379252892826</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3010723608477454</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.280086342931624</v>
+      </c>
+      <c r="K10" s="4">
+        <v>84.36025474019387</v>
+      </c>
+      <c r="L10" s="4">
+        <v>82.66988750852768</v>
+      </c>
+      <c r="M10" s="5">
+        <v>141</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1918966.547489166</v>
+      </c>
+      <c r="O10" s="4">
+        <v>86.95303581898438</v>
+      </c>
+      <c r="P10" s="5">
+        <v>22069</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>65.95744680851064</v>
+      </c>
+      <c r="C11" s="3">
+        <v>7.801418439716312</v>
+      </c>
+      <c r="D11" s="3">
+        <v>26.24113475177305</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2.127659574468085</v>
+      </c>
+      <c r="F11" s="3">
+        <v>10.63829787234043</v>
+      </c>
+      <c r="G11" s="3">
+        <v>13.47517730496454</v>
+      </c>
+      <c r="H11" s="4">
+        <v>1.285955763290779</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.9206735247342821</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1.317050517337244</v>
+      </c>
+      <c r="K11" s="4">
+        <v>71.57885849375218</v>
+      </c>
+      <c r="L11" s="4">
+        <v>82.06252875751666</v>
+      </c>
+      <c r="M11" s="5">
+        <v>141</v>
+      </c>
+      <c r="N11" s="5">
+        <v>645436.5818500519</v>
+      </c>
+      <c r="O11" s="4">
+        <v>39.67034922249857</v>
+      </c>
+      <c r="P11" s="5">
+        <v>16270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>80.85106382978722</v>
+      </c>
+      <c r="C12" s="3">
+        <v>4.964539007092199</v>
+      </c>
+      <c r="D12" s="3">
+        <v>14.18439716312057</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.418439716312057</v>
+      </c>
+      <c r="F12" s="3">
+        <v>3.546099290780142</v>
+      </c>
+      <c r="G12" s="3">
+        <v>9.219858156028367</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.9229184939413063</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.5711516217846304</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.9597588600911765</v>
+      </c>
+      <c r="K12" s="4">
+        <v>78.37361895112664</v>
+      </c>
+      <c r="L12" s="4">
+        <v>87.17573420914796</v>
+      </c>
+      <c r="M12" s="5">
+        <v>141</v>
+      </c>
+      <c r="N12" s="5">
+        <v>318362.0235919952</v>
+      </c>
+      <c r="O12" s="4">
+        <v>18.81461045990162</v>
+      </c>
+      <c r="P12" s="5">
+        <v>16921</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>70.92198581560284</v>
+      </c>
+      <c r="C13" s="3">
+        <v>12.05673758865248</v>
+      </c>
+      <c r="D13" s="3">
+        <v>17.02127659574468</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.418439716312057</v>
+      </c>
+      <c r="F13" s="3">
+        <v>4.964539007092199</v>
+      </c>
+      <c r="G13" s="3">
+        <v>10.63829787234043</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1.102726788962264</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.818860626484949</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1.14418510880042</v>
+      </c>
+      <c r="K13" s="4">
+        <v>69.22492401215807</v>
+      </c>
+      <c r="L13" s="4">
+        <v>81.46310311453766</v>
+      </c>
+      <c r="M13" s="5">
+        <v>141</v>
+      </c>
+      <c r="N13" s="5">
+        <v>2068275.821208954</v>
+      </c>
+      <c r="O13" s="4">
+        <v>78.59683911111358</v>
+      </c>
+      <c r="P13" s="5">
+        <v>26315</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>95.74468085106383</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.7092198581560284</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3.546099290780142</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.7092198581560284</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2.836879432624114</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.3074865901115852</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.2633778455289246</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.2608395747798573</v>
+      </c>
+      <c r="K14" s="4">
+        <v>92.49023013460702</v>
+      </c>
+      <c r="L14" s="4">
+        <v>94.15948720389824</v>
+      </c>
+      <c r="M14" s="5">
+        <v>141</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1727644.520521164</v>
+      </c>
+      <c r="O14" s="4">
+        <v>218.6061648135093</v>
+      </c>
+      <c r="P14" s="5">
+        <v>7903</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>92.90780141843972</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3.546099290780142</v>
+      </c>
+      <c r="D15" s="3">
+        <v>3.546099290780142</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2.836879432624114</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.7092198581560284</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.3271953208499491</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2550598005967033</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2955879723014122</v>
+      </c>
+      <c r="K15" s="4">
+        <v>87.45887007285144</v>
+      </c>
+      <c r="L15" s="4">
+        <v>91.24684658955492</v>
+      </c>
+      <c r="M15" s="5">
+        <v>141</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2954267.071008682</v>
+      </c>
+      <c r="O15" s="4">
+        <v>204.9155213295888</v>
+      </c>
+      <c r="P15" s="5">
+        <v>14417</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>94.32624113475178</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3.546099290780142</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2.127659574468085</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1.418439716312057</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.7092198581560284</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.3083734573880253</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.2862034111090005</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.2742116866314186</v>
+      </c>
+      <c r="K16" s="4">
+        <v>88.35239060163011</v>
+      </c>
+      <c r="L16" s="4">
+        <v>91.72092912561205</v>
+      </c>
+      <c r="M16" s="5">
+        <v>141</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1329634.772777557</v>
+      </c>
+      <c r="O16" s="4">
+        <v>97.92567187933108</v>
+      </c>
+      <c r="P16" s="5">
+        <v>13578</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>72.3404255319149</v>
+      </c>
+      <c r="C17" s="3">
+        <v>9.929078014184398</v>
+      </c>
+      <c r="D17" s="3">
+        <v>17.73049645390071</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.418439716312057</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4.25531914893617</v>
+      </c>
+      <c r="G17" s="3">
+        <v>12.05673758865248</v>
+      </c>
+      <c r="H17" s="4">
+        <v>1.110746921363174</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.767918533254194</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1.192286560043519</v>
+      </c>
+      <c r="K17" s="4">
+        <v>82.21932744729088</v>
+      </c>
+      <c r="L17" s="4">
+        <v>87.47608167928021</v>
+      </c>
+      <c r="M17" s="5">
+        <v>141</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1819041.528701782</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100.1950718095171</v>
+      </c>
+      <c r="P17" s="5">
+        <v>18155</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3206,10 +5382,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L3" s="5">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
@@ -3250,16 +5426,16 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -3294,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
@@ -3338,10 +5514,10 @@
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
@@ -3382,10 +5558,10 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
@@ -3426,7 +5602,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
         <v>8</v>
@@ -3470,10 +5646,10 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
@@ -3514,7 +5690,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
         <v>9</v>
@@ -3558,10 +5734,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -3605,7 +5781,7 @@
         <v>2</v>
       </c>
       <c r="L12" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
@@ -3646,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L13" s="5">
         <v>5</v>
@@ -3693,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
@@ -3734,10 +5910,10 @@
         <v>0</v>
       </c>
       <c r="K15" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15" s="5">
         <v>0</v>
@@ -3778,10 +5954,10 @@
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
@@ -3822,10 +5998,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17" s="5">
         <v>0</v>
@@ -3847,9 +6023,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>71</v>
+      </c>
+      <c r="C3" s="5">
+        <v>29</v>
+      </c>
+      <c r="D3" s="5">
+        <v>41</v>
+      </c>
+      <c r="E3" s="5">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5">
+        <v>24</v>
+      </c>
+      <c r="G3" s="5">
+        <v>8</v>
+      </c>
+      <c r="H3" s="5">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5">
+        <v>9</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>8</v>
+      </c>
+      <c r="L3" s="5">
+        <v>7</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>110</v>
+      </c>
+      <c r="C4" s="5">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5">
+        <v>20</v>
+      </c>
+      <c r="E4" s="5">
+        <v>6</v>
+      </c>
+      <c r="F4" s="5">
+        <v>13</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5">
+        <v>6</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>9</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>99</v>
+      </c>
+      <c r="C5" s="5">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5">
+        <v>32</v>
+      </c>
+      <c r="E5" s="5">
+        <v>3</v>
+      </c>
+      <c r="F5" s="5">
+        <v>10</v>
+      </c>
+      <c r="G5" s="5">
+        <v>19</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>10</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>96</v>
+      </c>
+      <c r="C6" s="5">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5">
+        <v>30</v>
+      </c>
+      <c r="E6" s="5">
+        <v>4</v>
+      </c>
+      <c r="F6" s="5">
+        <v>20</v>
+      </c>
+      <c r="G6" s="5">
+        <v>6</v>
+      </c>
+      <c r="H6" s="5">
+        <v>4</v>
+      </c>
+      <c r="I6" s="5">
+        <v>4</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>14</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>106</v>
+      </c>
+      <c r="C7" s="5">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5">
+        <v>31</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>4</v>
+      </c>
+      <c r="G7" s="5">
+        <v>25</v>
+      </c>
+      <c r="H7" s="5">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>4</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>99</v>
+      </c>
+      <c r="C8" s="5">
+        <v>25</v>
+      </c>
+      <c r="D8" s="5">
+        <v>17</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>8</v>
+      </c>
+      <c r="G8" s="5">
+        <v>8</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>8</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>83</v>
+      </c>
+      <c r="C9" s="5">
+        <v>26</v>
+      </c>
+      <c r="D9" s="5">
+        <v>32</v>
+      </c>
+      <c r="E9" s="5">
+        <v>9</v>
+      </c>
+      <c r="F9" s="5">
+        <v>22</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
+        <v>9</v>
+      </c>
+      <c r="I9" s="5">
+        <v>9</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>14</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>107</v>
+      </c>
+      <c r="C10" s="5">
+        <v>10</v>
+      </c>
+      <c r="D10" s="5">
+        <v>24</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <v>23</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>9</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>93</v>
+      </c>
+      <c r="C11" s="5">
+        <v>11</v>
+      </c>
+      <c r="D11" s="5">
+        <v>37</v>
+      </c>
+      <c r="E11" s="5">
+        <v>3</v>
+      </c>
+      <c r="F11" s="5">
+        <v>15</v>
+      </c>
+      <c r="G11" s="5">
+        <v>19</v>
+      </c>
+      <c r="H11" s="5">
+        <v>3</v>
+      </c>
+      <c r="I11" s="5">
+        <v>3</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>15</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>114</v>
+      </c>
+      <c r="C12" s="5">
+        <v>7</v>
+      </c>
+      <c r="D12" s="5">
+        <v>20</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2</v>
+      </c>
+      <c r="F12" s="5">
+        <v>5</v>
+      </c>
+      <c r="G12" s="5">
+        <v>13</v>
+      </c>
+      <c r="H12" s="5">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5">
+        <v>2</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>2</v>
+      </c>
+      <c r="L12" s="5">
+        <v>3</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>100</v>
+      </c>
+      <c r="C13" s="5">
+        <v>17</v>
+      </c>
+      <c r="D13" s="5">
+        <v>24</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5">
+        <v>7</v>
+      </c>
+      <c r="G13" s="5">
+        <v>15</v>
+      </c>
+      <c r="H13" s="5">
+        <v>2</v>
+      </c>
+      <c r="I13" s="5">
+        <v>2</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>2</v>
+      </c>
+      <c r="L13" s="5">
+        <v>5</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>135</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>5</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5">
+        <v>4</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5">
+        <v>1</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>4</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>131</v>
+      </c>
+      <c r="C15" s="5">
+        <v>5</v>
+      </c>
+      <c r="D15" s="5">
+        <v>5</v>
+      </c>
+      <c r="E15" s="5">
+        <v>4</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>4</v>
+      </c>
+      <c r="I15" s="5">
+        <v>4</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>133</v>
+      </c>
+      <c r="C16" s="5">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5">
+        <v>3</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>2</v>
+      </c>
+      <c r="I16" s="5">
+        <v>2</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>102</v>
+      </c>
+      <c r="C17" s="5">
+        <v>14</v>
+      </c>
+      <c r="D17" s="5">
+        <v>25</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2</v>
+      </c>
+      <c r="F17" s="5">
+        <v>6</v>
+      </c>
+      <c r="G17" s="5">
+        <v>17</v>
+      </c>
+      <c r="H17" s="5">
+        <v>2</v>
+      </c>
+      <c r="I17" s="5">
+        <v>2</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>2</v>
+      </c>
+      <c r="L17" s="5">
+        <v>4</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6791,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6833,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,132 +6864,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>2.05021267262937</v>
+        <v>1.214694463462539</v>
       </c>
       <c r="C3" s="4">
-        <v>1.019012332600176</v>
+        <v>0.5738380118655722</v>
       </c>
       <c r="D3" s="4">
-        <v>2.106471720646523</v>
+        <v>1.390367635605044</v>
       </c>
       <c r="E3" s="4">
-        <v>69.98046026921403</v>
+        <v>49.99131567520625</v>
       </c>
       <c r="F3" s="4">
-        <v>81.73639868627623</v>
+        <v>65.74015897948503</v>
       </c>
       <c r="G3" s="5">
         <v>47</v>
       </c>
       <c r="H3" s="5">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J3" s="5">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M3" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.6409532567192602</v>
+      </c>
+      <c r="O3" s="5">
+        <v>18</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.991267466172714</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3416330937137799</v>
+      </c>
+      <c r="R3" s="5">
+        <v>17</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.214694463462539</v>
+        <v>1.916350181973359</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5738380118655722</v>
+        <v>0.98423386615154</v>
       </c>
       <c r="D4" s="4">
-        <v>1.390367635605044</v>
+        <v>1.954024045491311</v>
       </c>
       <c r="E4" s="4">
-        <v>49.99131567520625</v>
+        <v>55.39875524677944</v>
       </c>
       <c r="F4" s="4">
-        <v>65.74015897948503</v>
+        <v>71.4431910133748</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I4" s="5">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J4" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K4" s="5">
         <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>8</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.766094359062572</v>
+      </c>
+      <c r="O4" s="5">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.387741008144039</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8840964060680003</v>
+      </c>
+      <c r="R4" s="5">
+        <v>26</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.916350181973359</v>
+        <v>2.05021267262937</v>
       </c>
       <c r="C5" s="4">
-        <v>0.98423386615154</v>
+        <v>1.019012332600176</v>
       </c>
       <c r="D5" s="4">
-        <v>1.954024045491311</v>
+        <v>2.106471720646523</v>
       </c>
       <c r="E5" s="4">
-        <v>55.39875524677944</v>
+        <v>69.98046026921403</v>
       </c>
       <c r="F5" s="4">
-        <v>71.4431910133748</v>
+        <v>81.73639868627623</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>21</v>
+      </c>
+      <c r="K5" s="5">
+        <v>5</v>
+      </c>
+      <c r="L5" s="5">
         <v>11</v>
       </c>
-      <c r="J5" s="5">
-        <v>14</v>
-      </c>
-      <c r="K5" s="5">
-        <v>2</v>
-      </c>
-      <c r="L5" s="5">
-        <v>4</v>
-      </c>
       <c r="M5" s="5">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.332918296894722</v>
+      </c>
+      <c r="O5" s="5">
+        <v>31</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.453823721977243</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6626499254959582</v>
+      </c>
+      <c r="R5" s="5">
+        <v>28</v>
+      </c>
+      <c r="S5" s="5">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7072,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7091,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7133,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,132 +7164,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.316421982841619</v>
+        <v>0.7545308322448383</v>
       </c>
       <c r="C3" s="4">
-        <v>1.079014867921541</v>
+        <v>0.7208639172901766</v>
       </c>
       <c r="D3" s="4">
-        <v>1.137832808298086</v>
+        <v>0.672300041718835</v>
       </c>
       <c r="E3" s="4">
-        <v>72.53003328991186</v>
+        <v>61.00303951367783</v>
       </c>
       <c r="F3" s="4">
-        <v>86.70307963253912</v>
+        <v>77.56818506354493</v>
       </c>
       <c r="G3" s="5">
         <v>47</v>
       </c>
       <c r="H3" s="5">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
         <v>10</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.7546032606756954</v>
+      </c>
+      <c r="O3" s="5">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6159488826781693</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4872109944252669</v>
+      </c>
+      <c r="R3" s="5">
+        <v>36</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7545308322448383</v>
+        <v>1.796406767310881</v>
       </c>
       <c r="C4" s="4">
-        <v>0.7208639172901766</v>
+        <v>1.602355277187598</v>
       </c>
       <c r="D4" s="4">
-        <v>0.672300041718835</v>
+        <v>1.669407828791183</v>
       </c>
       <c r="E4" s="4">
-        <v>61.00303951367783</v>
+        <v>56.41047908525113</v>
       </c>
       <c r="F4" s="4">
-        <v>77.56818506354493</v>
+        <v>73.83026322052461</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
+        <v>8</v>
+      </c>
+      <c r="J4" s="5">
+        <v>21</v>
+      </c>
+      <c r="K4" s="5">
         <v>3</v>
       </c>
-      <c r="J4" s="5">
-        <v>10</v>
-      </c>
-      <c r="K4" s="5">
-        <v>2</v>
-      </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>15</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.920016860514944</v>
+      </c>
+      <c r="O4" s="5">
+        <v>33</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.691708900107349</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3509700502193467</v>
+      </c>
+      <c r="R4" s="5">
+        <v>33</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.796406767310881</v>
+        <v>1.316421982841619</v>
       </c>
       <c r="C5" s="4">
-        <v>1.602355277187598</v>
+        <v>1.079014867921541</v>
       </c>
       <c r="D5" s="4">
-        <v>1.669407828791183</v>
+        <v>1.137832808298086</v>
       </c>
       <c r="E5" s="4">
-        <v>56.41047908525113</v>
+        <v>72.53003328991186</v>
       </c>
       <c r="F5" s="4">
-        <v>73.83026322052461</v>
+        <v>86.70307963253912</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="I5" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.189156844464183</v>
+      </c>
+      <c r="O5" s="5">
+        <v>42</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.805013040795155</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6048236732621839</v>
+      </c>
+      <c r="R5" s="5">
+        <v>41</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7372,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7391,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7433,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,25 +7464,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.534050807339496</v>
+        <v>0.8204937169469091</v>
       </c>
       <c r="C3" s="4">
-        <v>0.561547611366251</v>
+        <v>0.5480007396431574</v>
       </c>
       <c r="D3" s="4">
-        <v>1.506687840406735</v>
+        <v>0.8655244895019077</v>
       </c>
       <c r="E3" s="4">
-        <v>81.48936170212792</v>
+        <v>68.14155449413819</v>
       </c>
       <c r="F3" s="4">
-        <v>89.50164215336163</v>
+        <v>79.31005759436337</v>
       </c>
       <c r="G3" s="5">
         <v>47</v>
@@ -4372,105 +7509,159 @@
         <v>32</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J3" s="5">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>4</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.7627229089898466</v>
+      </c>
+      <c r="O3" s="5">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8054292117150814</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6164491271050745</v>
+      </c>
+      <c r="R3" s="5">
+        <v>33</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8204937169469091</v>
+        <v>1.3726007227922</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5480007396431574</v>
+        <v>0.3152225851058406</v>
       </c>
       <c r="D4" s="4">
-        <v>0.8655244895019077</v>
+        <v>1.373516617217068</v>
       </c>
       <c r="E4" s="4">
-        <v>68.14155449413819</v>
+        <v>68.48241424229259</v>
       </c>
       <c r="F4" s="4">
-        <v>79.31005759436337</v>
+        <v>79.72535579989531</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
+        <v>27</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="5">
+        <v>16</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>12</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.189337325845232</v>
+      </c>
+      <c r="O4" s="5">
+        <v>39</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.487755493928858</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.032840754025461</v>
+      </c>
+      <c r="R4" s="5">
         <v>32</v>
       </c>
-      <c r="I4" s="5">
-        <v>5</v>
-      </c>
-      <c r="J4" s="5">
-        <v>10</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>6</v>
-      </c>
-      <c r="M4" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="S4" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.3726007227922</v>
+        <v>1.534050807339496</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3152225851058406</v>
+        <v>0.561547611366251</v>
       </c>
       <c r="D5" s="4">
-        <v>1.373516617217068</v>
+        <v>1.506687840406735</v>
       </c>
       <c r="E5" s="4">
-        <v>68.48241424229259</v>
+        <v>81.48936170212792</v>
       </c>
       <c r="F5" s="4">
-        <v>79.72535579989531</v>
+        <v>89.50164215336163</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I5" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
         <v>2</v>
       </c>
       <c r="M5" s="5">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.22998805757707</v>
+      </c>
+      <c r="O5" s="5">
+        <v>43</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.469012977666904</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.895028218334031</v>
+      </c>
+      <c r="R5" s="5">
+        <v>34</v>
+      </c>
+      <c r="S5" s="5">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7672,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7691,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7733,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,34 +7764,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.236846193704278</v>
+        <v>0.7870295653106331</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8384559958461014</v>
+        <v>0.6551128220339422</v>
       </c>
       <c r="D3" s="4">
-        <v>1.220478228821602</v>
+        <v>0.7562799877421911</v>
       </c>
       <c r="E3" s="4">
-        <v>78.58662613981721</v>
+        <v>69.05557967868015</v>
       </c>
       <c r="F3" s="4">
-        <v>88.8645342472267</v>
+        <v>81.09405492883968</v>
       </c>
       <c r="G3" s="5">
         <v>47</v>
       </c>
       <c r="H3" s="5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
         <v>12</v>
@@ -4594,96 +7818,150 @@
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M3" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>4</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.7586684513303984</v>
+      </c>
+      <c r="O3" s="5">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6897172515029397</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6064034814413113</v>
+      </c>
+      <c r="R3" s="5">
+        <v>36</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7870295653106331</v>
+        <v>1.08520272110777</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6551128220339422</v>
+        <v>0.6420054851127394</v>
       </c>
       <c r="D4" s="4">
-        <v>0.7562799877421911</v>
+        <v>1.097631816994819</v>
       </c>
       <c r="E4" s="4">
-        <v>69.05557967868015</v>
+        <v>56.64423216094959</v>
       </c>
       <c r="F4" s="4">
-        <v>81.09405492883968</v>
+        <v>68.96353943548046</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J4" s="5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.9467560974037406</v>
+      </c>
+      <c r="O4" s="5">
+        <v>25</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9802797807614826</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5866795059409197</v>
+      </c>
+      <c r="R4" s="5">
+        <v>23</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.08520272110777</v>
+        <v>1.236846193704278</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6420054851127394</v>
+        <v>0.8384559958461014</v>
       </c>
       <c r="D5" s="4">
-        <v>1.097631816994819</v>
+        <v>1.220478228821602</v>
       </c>
       <c r="E5" s="4">
-        <v>56.64423216094959</v>
+        <v>78.58662613981721</v>
       </c>
       <c r="F5" s="4">
-        <v>68.96353943548046</v>
+        <v>88.8645342472267</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I5" s="5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>5</v>
+      </c>
+      <c r="M5" s="5">
+        <v>7</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.079994520892309</v>
+      </c>
+      <c r="O5" s="5">
+        <v>41</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8897526150877952</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6971208456280824</v>
+      </c>
+      <c r="R5" s="5">
+        <v>37</v>
+      </c>
+      <c r="S5" s="5">
         <v>4</v>
       </c>
-      <c r="L5" s="5">
-        <v>7</v>
-      </c>
-      <c r="M5" s="5">
-        <v>4</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7972,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7991,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8033,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,116 +8064,170 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.246658934850007</v>
+        <v>1.020657236052334</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4086668804045931</v>
+        <v>0.2663146523919115</v>
       </c>
       <c r="D3" s="4">
-        <v>1.293553155344272</v>
+        <v>1.119820778711247</v>
       </c>
       <c r="E3" s="4">
-        <v>89.96381531335879</v>
+        <v>82.40700535533411</v>
       </c>
       <c r="F3" s="4">
-        <v>93.87786186872459</v>
+        <v>88.5270598314998</v>
       </c>
       <c r="G3" s="5">
         <v>47</v>
       </c>
       <c r="H3" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>13</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.954521056509479</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.193898891272102</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.8969963787681414</v>
+      </c>
+      <c r="R3" s="5">
+        <v>36</v>
+      </c>
+      <c r="S3" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.020657236052334</v>
+        <v>1.218161858836054</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2663146523919115</v>
+        <v>0.3192894197926204</v>
       </c>
       <c r="D4" s="4">
-        <v>1.119820778711247</v>
+        <v>1.29788723193929</v>
       </c>
       <c r="E4" s="4">
-        <v>82.40700535533411</v>
+        <v>77.50687509046146</v>
       </c>
       <c r="F4" s="4">
-        <v>88.5270598314998</v>
+        <v>85.87724308629431</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
         <v>13</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>1.102368709866022</v>
+      </c>
+      <c r="O4" s="5">
+        <v>42</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.335981947380894</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8940850475884609</v>
+      </c>
+      <c r="R4" s="5">
+        <v>35</v>
+      </c>
+      <c r="S4" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.218161858836054</v>
+        <v>1.246658934850007</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3192894197926204</v>
+        <v>0.4086668804045931</v>
       </c>
       <c r="D5" s="4">
-        <v>1.29788723193929</v>
+        <v>1.293553155344272</v>
       </c>
       <c r="E5" s="4">
-        <v>77.50687509046146</v>
+        <v>89.96381531335879</v>
       </c>
       <c r="F5" s="4">
-        <v>85.87724308629431</v>
+        <v>93.87786186872459</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>13</v>
@@ -4894,9 +8241,27 @@
       <c r="M5" s="5">
         <v>11</v>
       </c>
+      <c r="N5" s="4">
+        <v>1.136576230037624</v>
+      </c>
+      <c r="O5" s="5">
+        <v>45</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.427722530399969</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.9701585029689158</v>
+      </c>
+      <c r="R5" s="5">
+        <v>35</v>
+      </c>
+      <c r="S5" s="5">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8272,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.30525729542627</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.8339825978105095</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.386310769283565</v>
-      </c>
-      <c r="E3" s="4">
-        <v>87.69214068606145</v>
-      </c>
-      <c r="F3" s="4">
-        <v>91.406778047503</v>
-      </c>
-      <c r="G3" s="5">
-        <v>47</v>
-      </c>
-      <c r="H3" s="5">
-        <v>36</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>11</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.8767570532616891</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6067724178983758</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.9233687322290283</v>
-      </c>
-      <c r="E4" s="4">
-        <v>75.87494572297007</v>
-      </c>
-      <c r="F4" s="4">
-        <v>81.6164500928182</v>
-      </c>
-      <c r="G4" s="5">
-        <v>47</v>
-      </c>
-      <c r="H4" s="5">
-        <v>31</v>
-      </c>
-      <c r="I4" s="5">
-        <v>7</v>
-      </c>
-      <c r="J4" s="5">
-        <v>9</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>4</v>
-      </c>
-      <c r="M4" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.194847695675462</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.530617475163084</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.384450816784594</v>
-      </c>
-      <c r="E5" s="4">
-        <v>62.46200607902752</v>
-      </c>
-      <c r="F5" s="4">
-        <v>72.41896330144269</v>
-      </c>
-      <c r="G5" s="5">
-        <v>47</v>
-      </c>
-      <c r="H5" s="5">
-        <v>24</v>
-      </c>
-      <c r="I5" s="5">
-        <v>18</v>
-      </c>
-      <c r="J5" s="5">
-        <v>5</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>2</v>
-      </c>
-      <c r="M5" s="5">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.435427330618969</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.9175416369784476</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.407736242434537</v>
-      </c>
-      <c r="E3" s="4">
-        <v>78.51715154146812</v>
-      </c>
-      <c r="F3" s="4">
-        <v>87.40539768670317</v>
-      </c>
-      <c r="G3" s="5">
-        <v>47</v>
-      </c>
-      <c r="H3" s="5">
-        <v>28</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>19</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>8</v>
-      </c>
-      <c r="M3" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.8110501244456944</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.7121386575232733</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.8762548210642443</v>
-      </c>
-      <c r="E4" s="4">
-        <v>59.58242871616751</v>
-      </c>
-      <c r="F4" s="4">
-        <v>72.21143319529706</v>
-      </c>
-      <c r="G4" s="5">
-        <v>47</v>
-      </c>
-      <c r="H4" s="5">
-        <v>27</v>
-      </c>
-      <c r="I4" s="5">
-        <v>12</v>
-      </c>
-      <c r="J4" s="5">
-        <v>8</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>7</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.585551136820617</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.9067214583845384</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.339848148825366</v>
-      </c>
-      <c r="E5" s="4">
-        <v>51.56028368794322</v>
-      </c>
-      <c r="F5" s="4">
-        <v>67.82378980436894</v>
-      </c>
-      <c r="G5" s="5">
-        <v>47</v>
-      </c>
-      <c r="H5" s="5">
-        <v>16</v>
-      </c>
-      <c r="I5" s="5">
-        <v>14</v>
-      </c>
-      <c r="J5" s="5">
-        <v>17</v>
-      </c>
-      <c r="K5" s="5">
-        <v>7</v>
-      </c>
-      <c r="L5" s="5">
-        <v>7</v>
-      </c>
-      <c r="M5" s="5">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/BackSingle2018.xlsx
+++ b/public/downloads/BackSingle2018.xlsx
@@ -1557,22 +1557,22 @@
         <v>5</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7748966852712592</v>
+        <v>0.4860735547727302</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7634253370149643</v>
+        <v>0.7066785755131297</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6664614034207113</v>
+        <v>0.4989076532479662</v>
       </c>
       <c r="R3" s="5">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -1616,16 +1616,16 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6444260867928325</v>
+        <v>0.5498899914400965</v>
       </c>
       <c r="O4" s="5">
         <v>27</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9184640568242065</v>
+        <v>0.9160529390320324</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4547181116203126</v>
+        <v>0.4321795341973947</v>
       </c>
       <c r="R4" s="5">
         <v>26</v>
@@ -1675,22 +1675,22 @@
         <v>8</v>
       </c>
       <c r="N5" s="4">
-        <v>1.101166942049926</v>
+        <v>0.8865836606525122</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.9625656055913369</v>
+        <v>0.9243049054877834</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6070942746090356</v>
+        <v>0.5053762463086995</v>
       </c>
       <c r="R5" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S5" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.6089381792141837</v>
+        <v>0.4610432660992956</v>
       </c>
       <c r="O3" s="5">
         <v>27</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7034575813367234</v>
+        <v>0.6973381781908369</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5503931943900676</v>
+        <v>0.5397409000250062</v>
       </c>
       <c r="R3" s="5">
         <v>27</v>
@@ -1916,16 +1916,16 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>1.131688956146478</v>
+        <v>1.172119181406742</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>1.344216851012695</v>
+        <v>1.350801028387476</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5993366754222095</v>
+        <v>0.597208768829564</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -1975,22 +1975,22 @@
         <v>10</v>
       </c>
       <c r="N5" s="4">
-        <v>1.143271876687179</v>
+        <v>1.017777554515305</v>
       </c>
       <c r="O5" s="5">
         <v>38</v>
       </c>
       <c r="P5" s="4">
-        <v>1.136192441521072</v>
+        <v>1.126720207110319</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.8608720656298248</v>
+        <v>0.8905749379384935</v>
       </c>
       <c r="R5" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.0344012044379975</v>
+        <v>0.05410824898142153</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3012591198822419</v>
+        <v>0.3005700427620925</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2598343659024376</v>
+        <v>0.2594821553440045</v>
       </c>
       <c r="R3" s="5">
         <v>36</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2756294876654406</v>
+        <v>0.3012009551837664</v>
       </c>
       <c r="O4" s="5">
         <v>33</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3878119325239524</v>
+        <v>0.3885003183768481</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2519578915093679</v>
+        <v>0.2498387480249071</v>
       </c>
       <c r="R4" s="5">
         <v>33</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1192052031840599</v>
+        <v>0.1422728169805794</v>
       </c>
       <c r="O5" s="5">
         <v>38</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4483427234616537</v>
+        <v>0.4450366177374464</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3827919741687333</v>
+        <v>0.3817380557462297</v>
       </c>
       <c r="R5" s="5">
         <v>38</v>
@@ -2457,22 +2457,22 @@
         <v>7</v>
       </c>
       <c r="N3" s="4">
-        <v>1.018359458825591</v>
+        <v>0.5203835144411642</v>
       </c>
       <c r="O3" s="5">
         <v>34</v>
       </c>
       <c r="P3" s="4">
-        <v>1.196703691354235</v>
+        <v>1.096501144407932</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.740438088329608</v>
+        <v>0.3524177863429806</v>
       </c>
       <c r="R3" s="5">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="S3" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -2516,22 +2516,22 @@
         <v>11</v>
       </c>
       <c r="N4" s="4">
-        <v>1.554395866813762</v>
+        <v>0.7711498224252864</v>
       </c>
       <c r="O4" s="5">
         <v>35</v>
       </c>
       <c r="P4" s="4">
-        <v>1.359926096817366</v>
+        <v>1.111868147694641</v>
       </c>
       <c r="Q4" s="4">
-        <v>1.08453935948311</v>
+        <v>0.3423671657822706</v>
       </c>
       <c r="R4" s="5">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="S4" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -2575,22 +2575,22 @@
         <v>12</v>
       </c>
       <c r="N5" s="4">
-        <v>1.305764966586477</v>
+        <v>0.786875838002743</v>
       </c>
       <c r="O5" s="5">
         <v>43</v>
       </c>
       <c r="P5" s="4">
-        <v>1.301237501700734</v>
+        <v>1.174025563440777</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.9342369089634123</v>
+        <v>0.5204383844802853</v>
       </c>
       <c r="R5" s="5">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S5" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2757,16 +2757,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5647150715965751</v>
+        <v>0.2705950630543157</v>
       </c>
       <c r="O3" s="5">
         <v>43</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7023588000728936</v>
+        <v>0.6280957204230521</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5002360472362449</v>
+        <v>0.4056239284341245</v>
       </c>
       <c r="R3" s="5">
         <v>40</v>
@@ -2816,16 +2816,16 @@
         <v>6</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6996515413550923</v>
+        <v>0.2335465432224737</v>
       </c>
       <c r="O4" s="5">
         <v>40</v>
       </c>
       <c r="P4" s="4">
-        <v>1.118970351739674</v>
+        <v>1.017941025695476</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5637614908317532</v>
+        <v>0.2458866878964192</v>
       </c>
       <c r="R4" s="5">
         <v>34</v>
@@ -2875,22 +2875,22 @@
         <v>7</v>
       </c>
       <c r="N5" s="4">
-        <v>0.8374977027656108</v>
+        <v>0.4925530382106444</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.947426330011351</v>
+        <v>0.891622516444976</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6483488076429611</v>
+        <v>0.5006552649491334</v>
       </c>
       <c r="R5" s="5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S5" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3057,22 +3057,22 @@
         <v>9</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7542748793563251</v>
+        <v>0.2650556033158864</v>
       </c>
       <c r="O3" s="5">
         <v>42</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9565939324084106</v>
+        <v>0.8418899150472769</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7734238647298937</v>
+        <v>0.3477518890705035</v>
       </c>
       <c r="R3" s="5">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S3" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -3116,22 +3116,22 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>0.8345364788141784</v>
+        <v>0.5007488738183383</v>
       </c>
       <c r="O4" s="5">
         <v>28</v>
       </c>
       <c r="P4" s="4">
-        <v>0.969444158851851</v>
+        <v>0.8929122120480315</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5742036787370358</v>
+        <v>0.3070369770440493</v>
       </c>
       <c r="R4" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -3175,22 +3175,22 @@
         <v>14</v>
       </c>
       <c r="N5" s="4">
-        <v>1.318331698618082</v>
+        <v>0.6392435092611777</v>
       </c>
       <c r="O5" s="5">
         <v>45</v>
       </c>
       <c r="P5" s="4">
-        <v>1.382142275626529</v>
+        <v>1.166556877920715</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.030834157306298</v>
+        <v>0.3645793953664026</v>
       </c>
       <c r="R5" s="5">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="S5" s="5">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3357,16 +3357,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.02467566288585983</v>
+        <v>0.08326088733250003</v>
       </c>
       <c r="O3" s="5">
         <v>45</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2001170112105181</v>
+        <v>0.1944949596931684</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1999764416644108</v>
+        <v>0.1941045211907345</v>
       </c>
       <c r="R3" s="5">
         <v>45</v>
@@ -3416,16 +3416,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1442828888631373</v>
+        <v>0.169868687616173</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3249220802192047</v>
+        <v>0.3249084446904309</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2242489145290223</v>
+        <v>0.2230975263655013</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -3475,16 +3475,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.03664009310313499</v>
+        <v>0.01087258055758866</v>
       </c>
       <c r="O5" s="5">
         <v>45</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3974206789050327</v>
+        <v>0.3968724339572552</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3659081803933406</v>
+        <v>0.3653355690034397</v>
       </c>
       <c r="R5" s="5">
         <v>45</v>
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3296848563039373</v>
+        <v>-0.353111150821384</v>
       </c>
       <c r="O3" s="5">
         <v>46</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2030031497407492</v>
+        <v>0.2012543056984494</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1929018033141893</v>
+        <v>0.1916242081952623</v>
       </c>
       <c r="R3" s="5">
         <v>46</v>
@@ -3716,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3075072341801846</v>
+        <v>-0.4665831858520093</v>
       </c>
       <c r="O4" s="5">
         <v>39</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4736065224528891</v>
+        <v>0.4541242715779973</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3099326541151642</v>
+        <v>0.2843537817801715</v>
       </c>
       <c r="R4" s="5">
         <v>39</v>
@@ -3775,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2238735119170081</v>
+        <v>-0.2113374699174102</v>
       </c>
       <c r="O5" s="5">
         <v>46</v>
       </c>
       <c r="P5" s="4">
-        <v>0.304976290356209</v>
+        <v>0.3047959181334687</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2706951612005223</v>
+        <v>0.2702383451903398</v>
       </c>
       <c r="R5" s="5">
         <v>46</v>
@@ -3957,16 +3957,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1503805259377247</v>
+        <v>0.1926768939279389</v>
       </c>
       <c r="O3" s="5">
         <v>46</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2389093517219295</v>
+        <v>0.2366565503016605</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2420254649474827</v>
+        <v>0.2406431758439517</v>
       </c>
       <c r="R3" s="5">
         <v>46</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3100026498426822</v>
+        <v>0.3350904755279851</v>
       </c>
       <c r="O4" s="5">
         <v>42</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2844680906301786</v>
+        <v>0.2850018741553978</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2455546012717974</v>
+        <v>0.2455546012717973</v>
       </c>
       <c r="R4" s="5">
         <v>42</v>
@@ -4075,16 +4075,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.06964174380740845</v>
+        <v>0.0994909378850366</v>
       </c>
       <c r="O5" s="5">
         <v>45</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4017429298119676</v>
+        <v>0.400499953895424</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3693019785888308</v>
+        <v>0.3680037592982185</v>
       </c>
       <c r="R5" s="5">
         <v>45</v>
@@ -4257,16 +4257,16 @@
         <v>5</v>
       </c>
       <c r="N3" s="4">
-        <v>0.233830676355712</v>
+        <v>-0.07833488513640674</v>
       </c>
       <c r="O3" s="5">
         <v>39</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7982550871973439</v>
+        <v>0.7333540159681565</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5331812138530291</v>
+        <v>0.3241076065833422</v>
       </c>
       <c r="R3" s="5">
         <v>34</v>
@@ -4316,22 +4316,22 @@
         <v>9</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7361248575750742</v>
+        <v>-0.01050216251947944</v>
       </c>
       <c r="O4" s="5">
         <v>37</v>
       </c>
       <c r="P4" s="4">
-        <v>1.349286565760216</v>
+        <v>1.08530997915043</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.9421993322352538</v>
+        <v>0.2889186691998381</v>
       </c>
       <c r="R4" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S4" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -4375,22 +4375,22 @@
         <v>7</v>
       </c>
       <c r="N5" s="4">
-        <v>0.415863675497418</v>
+        <v>-0.1040501031930319</v>
       </c>
       <c r="O5" s="5">
         <v>43</v>
       </c>
       <c r="P5" s="4">
-        <v>1.184699111131962</v>
+        <v>1.071234082241297</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.8429679099000625</v>
+        <v>0.4830931356099496</v>
       </c>
       <c r="R5" s="5">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="S5" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4503,13 +4503,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>50.35460992907801</v>
+        <v>48.22695035460993</v>
       </c>
       <c r="C3" s="3">
         <v>20.56737588652482</v>
       </c>
       <c r="D3" s="3">
-        <v>29.07801418439716</v>
+        <v>31.20567375886525</v>
       </c>
       <c r="E3" s="3">
         <v>6.382978723404255</v>
@@ -4518,16 +4518,16 @@
         <v>17.02127659574468</v>
       </c>
       <c r="G3" s="3">
-        <v>5.673758865248227</v>
+        <v>7.801418439716312</v>
       </c>
       <c r="H3" s="4">
-        <v>1.277610732097999</v>
+        <v>1.223225450787227</v>
       </c>
       <c r="I3" s="4">
-        <v>0.6668798178139308</v>
+        <v>0.4620779407690768</v>
       </c>
       <c r="J3" s="4">
-        <v>1.248243804712031</v>
+        <v>1.19795077221221</v>
       </c>
       <c r="K3" s="4">
         <v>58.4568437303999</v>
@@ -4571,13 +4571,13 @@
         <v>0.7092198581560284</v>
       </c>
       <c r="H4" s="4">
-        <v>0.7042236078602245</v>
+        <v>0.7066319542626591</v>
       </c>
       <c r="I4" s="4">
-        <v>0.4901761641845234</v>
+        <v>0.4875669267566991</v>
       </c>
       <c r="J4" s="4">
-        <v>0.494723055933136</v>
+        <v>0.4993939036953279</v>
       </c>
       <c r="K4" s="4">
         <v>63.31451729628017</v>
@@ -4603,13 +4603,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>70.21276595744681</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="C5" s="3">
         <v>7.092198581560284</v>
       </c>
       <c r="D5" s="3">
-        <v>22.69503546099291</v>
+        <v>26.24113475177305</v>
       </c>
       <c r="E5" s="3">
         <v>2.127659574468085</v>
@@ -4618,16 +4618,16 @@
         <v>7.092198581560284</v>
       </c>
       <c r="G5" s="3">
-        <v>13.47517730496454</v>
+        <v>17.02127659574468</v>
       </c>
       <c r="H5" s="4">
-        <v>1.254065894436948</v>
+        <v>1.084406402123161</v>
       </c>
       <c r="I5" s="4">
-        <v>0.8467139873397904</v>
+        <v>0.4446346399394838</v>
       </c>
       <c r="J5" s="4">
-        <v>1.17015495180058</v>
+        <v>1.026579694279794</v>
       </c>
       <c r="K5" s="4">
         <v>72.70444347951945</v>
@@ -4653,13 +4653,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>68.08510638297872</v>
+        <v>67.37588652482269</v>
       </c>
       <c r="C6" s="3">
         <v>10.63829787234043</v>
       </c>
       <c r="D6" s="3">
-        <v>21.27659574468085</v>
+        <v>21.98581560283688</v>
       </c>
       <c r="E6" s="3">
         <v>2.836879432624114</v>
@@ -4668,16 +4668,16 @@
         <v>14.18439716312057</v>
       </c>
       <c r="G6" s="3">
-        <v>4.25531914893617</v>
+        <v>4.964539007092199</v>
       </c>
       <c r="H6" s="4">
-        <v>0.8532498824507394</v>
+        <v>0.8011827048909763</v>
       </c>
       <c r="I6" s="4">
-        <v>0.6366419297579938</v>
+        <v>0.5770859586558129</v>
       </c>
       <c r="J6" s="4">
-        <v>0.7534536660334271</v>
+        <v>0.7290551630499131</v>
       </c>
       <c r="K6" s="4">
         <v>68.09547932648229</v>
@@ -4703,13 +4703,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>75.177304964539</v>
+        <v>70.92198581560284</v>
       </c>
       <c r="C7" s="3">
         <v>2.836879432624114</v>
       </c>
       <c r="D7" s="3">
-        <v>21.98581560283688</v>
+        <v>26.24113475177305</v>
       </c>
       <c r="E7" s="3">
         <v>1.418439716312057</v>
@@ -4718,16 +4718,16 @@
         <v>2.836879432624114</v>
       </c>
       <c r="G7" s="3">
-        <v>17.73049645390071</v>
+        <v>21.98581560283688</v>
       </c>
       <c r="H7" s="4">
-        <v>1.319201123017655</v>
+        <v>1.05404763409317</v>
       </c>
       <c r="I7" s="4">
-        <v>0.92019239533171</v>
+        <v>0.2961696307762031</v>
       </c>
       <c r="J7" s="4">
-        <v>1.328017371574598</v>
+        <v>1.10810205489063</v>
       </c>
       <c r="K7" s="4">
         <v>83.29256525305168</v>
@@ -4753,13 +4753,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>70.21276595744681</v>
+        <v>68.08510638297872</v>
       </c>
       <c r="C8" s="3">
         <v>17.73049645390071</v>
       </c>
       <c r="D8" s="3">
-        <v>12.05673758865248</v>
+        <v>14.18439716312057</v>
       </c>
       <c r="E8" s="3">
         <v>0.7092198581560284</v>
@@ -4768,16 +4768,16 @@
         <v>5.673758865248227</v>
       </c>
       <c r="G8" s="3">
-        <v>5.673758865248227</v>
+        <v>7.801418439716312</v>
       </c>
       <c r="H8" s="4">
-        <v>0.8814849998101693</v>
+        <v>0.8490121400109818</v>
       </c>
       <c r="I8" s="4">
-        <v>0.5880646712827915</v>
+        <v>0.4833285579139274</v>
       </c>
       <c r="J8" s="4">
-        <v>0.8888485023750241</v>
+        <v>0.8751543073833311</v>
       </c>
       <c r="K8" s="4">
         <v>75.34303082935307</v>
@@ -4803,13 +4803,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>58.86524822695035</v>
+        <v>59.57446808510638</v>
       </c>
       <c r="C9" s="3">
         <v>18.43971631205673</v>
       </c>
       <c r="D9" s="3">
-        <v>22.69503546099291</v>
+        <v>21.98581560283688</v>
       </c>
       <c r="E9" s="3">
         <v>6.382978723404255</v>
@@ -4818,16 +4818,16 @@
         <v>15.60283687943262</v>
       </c>
       <c r="G9" s="3">
-        <v>0.7092198581560284</v>
+        <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>1.06128895795683</v>
+        <v>1.058286471229544</v>
       </c>
       <c r="I9" s="4">
-        <v>0.7000033675886423</v>
+        <v>0.7114502208345195</v>
       </c>
       <c r="J9" s="4">
-        <v>0.7418137560579873</v>
+        <v>0.7537726210048212</v>
       </c>
       <c r="K9" s="4">
         <v>63.21995464852613</v>
@@ -4871,13 +4871,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.3791379252892826</v>
+        <v>0.3780356596254624</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3010723608477454</v>
+        <v>0.2999260036968489</v>
       </c>
       <c r="J10" s="4">
-        <v>0.280086342931624</v>
+        <v>0.2771876814282015</v>
       </c>
       <c r="K10" s="4">
         <v>84.36025474019387</v>
@@ -4903,13 +4903,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>65.95744680851064</v>
+        <v>60.28368794326241</v>
       </c>
       <c r="C11" s="3">
         <v>7.801418439716312</v>
       </c>
       <c r="D11" s="3">
-        <v>26.24113475177305</v>
+        <v>31.91489361702128</v>
       </c>
       <c r="E11" s="3">
         <v>2.127659574468085</v>
@@ -4918,16 +4918,16 @@
         <v>10.63829787234043</v>
       </c>
       <c r="G11" s="3">
-        <v>13.47517730496454</v>
+        <v>19.14893617021277</v>
       </c>
       <c r="H11" s="4">
-        <v>1.285955763290779</v>
+        <v>1.127464951847784</v>
       </c>
       <c r="I11" s="4">
-        <v>0.9206735247342821</v>
+        <v>0.4146932478078431</v>
       </c>
       <c r="J11" s="4">
-        <v>1.317050517337244</v>
+        <v>1.190757119392569</v>
       </c>
       <c r="K11" s="4">
         <v>71.57885849375218</v>
@@ -4953,13 +4953,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>80.85106382978722</v>
+        <v>80.1418439716312</v>
       </c>
       <c r="C12" s="3">
         <v>4.964539007092199</v>
       </c>
       <c r="D12" s="3">
-        <v>14.18439716312057</v>
+        <v>14.8936170212766</v>
       </c>
       <c r="E12" s="3">
         <v>1.418439716312057</v>
@@ -4968,16 +4968,16 @@
         <v>3.546099290780142</v>
       </c>
       <c r="G12" s="3">
-        <v>9.219858156028367</v>
+        <v>9.929078014184398</v>
       </c>
       <c r="H12" s="4">
-        <v>0.9229184939413063</v>
+        <v>0.8458864208545015</v>
       </c>
       <c r="I12" s="4">
-        <v>0.5711516217846304</v>
+        <v>0.390359821759818</v>
       </c>
       <c r="J12" s="4">
-        <v>0.9597588600911765</v>
+        <v>0.8897613217964103</v>
       </c>
       <c r="K12" s="4">
         <v>78.37361895112664</v>
@@ -5003,13 +5003,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="3">
-        <v>70.92198581560284</v>
+        <v>63.12056737588653</v>
       </c>
       <c r="C13" s="3">
         <v>12.05673758865248</v>
       </c>
       <c r="D13" s="3">
-        <v>17.02127659574468</v>
+        <v>24.82269503546099</v>
       </c>
       <c r="E13" s="3">
         <v>1.418439716312057</v>
@@ -5018,16 +5018,16 @@
         <v>4.964539007092199</v>
       </c>
       <c r="G13" s="3">
-        <v>10.63829787234043</v>
+        <v>18.43971631205673</v>
       </c>
       <c r="H13" s="4">
-        <v>1.102726788962264</v>
+        <v>0.9671196683386744</v>
       </c>
       <c r="I13" s="4">
-        <v>0.818860626484949</v>
+        <v>0.3426338531889077</v>
       </c>
       <c r="J13" s="4">
-        <v>1.14418510880042</v>
+        <v>1.037525212959678</v>
       </c>
       <c r="K13" s="4">
         <v>69.22492401215807</v>
@@ -5071,13 +5071,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.3074865901115852</v>
+        <v>0.3054252794469515</v>
       </c>
       <c r="I14" s="4">
-        <v>0.2633778455289246</v>
+        <v>0.2608458721865585</v>
       </c>
       <c r="J14" s="4">
-        <v>0.2608395747798573</v>
+        <v>0.2575954228027484</v>
       </c>
       <c r="K14" s="4">
         <v>92.49023013460702</v>
@@ -5121,13 +5121,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.3271953208499491</v>
+        <v>0.3200581651366385</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2550598005967033</v>
+        <v>0.2468356866043083</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2955879723014122</v>
+        <v>0.2998109979660964</v>
       </c>
       <c r="K15" s="4">
         <v>87.45887007285144</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.3083734573880253</v>
+        <v>0.3073861261174941</v>
       </c>
       <c r="I16" s="4">
-        <v>0.2862034111090005</v>
+        <v>0.285286079027497</v>
       </c>
       <c r="J16" s="4">
-        <v>0.2742116866314186</v>
+        <v>0.2712157469878087</v>
       </c>
       <c r="K16" s="4">
         <v>88.35239060163011</v>
@@ -5203,13 +5203,13 @@
         <v>31</v>
       </c>
       <c r="B17" s="3">
-        <v>72.3404255319149</v>
+        <v>68.79432624113475</v>
       </c>
       <c r="C17" s="3">
         <v>9.929078014184398</v>
       </c>
       <c r="D17" s="3">
-        <v>17.73049645390071</v>
+        <v>21.27659574468085</v>
       </c>
       <c r="E17" s="3">
         <v>1.418439716312057</v>
@@ -5218,16 +5218,16 @@
         <v>4.25531914893617</v>
       </c>
       <c r="G17" s="3">
-        <v>12.05673758865248</v>
+        <v>15.60283687943262</v>
       </c>
       <c r="H17" s="4">
-        <v>1.110746921363174</v>
+        <v>0.9632993591199611</v>
       </c>
       <c r="I17" s="4">
-        <v>0.767918533254194</v>
+        <v>0.3713158877090447</v>
       </c>
       <c r="J17" s="4">
-        <v>1.192286560043519</v>
+        <v>1.066880035564191</v>
       </c>
       <c r="K17" s="4">
         <v>82.21932744729088</v>
@@ -6110,13 +6110,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C3" s="5">
         <v>29</v>
       </c>
       <c r="D3" s="5">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E3" s="5">
         <v>9</v>
@@ -6125,7 +6125,7 @@
         <v>24</v>
       </c>
       <c r="G3" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H3" s="5">
         <v>9</v>
@@ -6198,13 +6198,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C5" s="5">
         <v>10</v>
       </c>
       <c r="D5" s="5">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E5" s="5">
         <v>3</v>
@@ -6213,7 +6213,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="5">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H5" s="5">
         <v>3</v>
@@ -6242,13 +6242,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" s="5">
         <v>15</v>
       </c>
       <c r="D6" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="5">
         <v>4</v>
@@ -6257,7 +6257,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" s="5">
         <v>4</v>
@@ -6286,13 +6286,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="5">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C7" s="5">
         <v>4</v>
       </c>
       <c r="D7" s="5">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E7" s="5">
         <v>2</v>
@@ -6301,7 +6301,7 @@
         <v>4</v>
       </c>
       <c r="G7" s="5">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H7" s="5">
         <v>2</v>
@@ -6330,13 +6330,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C8" s="5">
         <v>25</v>
       </c>
       <c r="D8" s="5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E8" s="5">
         <v>1</v>
@@ -6345,7 +6345,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H8" s="5">
         <v>1</v>
@@ -6374,13 +6374,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="5">
         <v>26</v>
       </c>
       <c r="D9" s="5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" s="5">
         <v>9</v>
@@ -6389,7 +6389,7 @@
         <v>22</v>
       </c>
       <c r="G9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="5">
         <v>9</v>
@@ -6462,13 +6462,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C11" s="5">
         <v>11</v>
       </c>
       <c r="D11" s="5">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E11" s="5">
         <v>3</v>
@@ -6477,7 +6477,7 @@
         <v>15</v>
       </c>
       <c r="G11" s="5">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H11" s="5">
         <v>3</v>
@@ -6506,13 +6506,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C12" s="5">
         <v>7</v>
       </c>
       <c r="D12" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" s="5">
         <v>2</v>
@@ -6521,7 +6521,7 @@
         <v>5</v>
       </c>
       <c r="G12" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="5">
         <v>2</v>
@@ -6550,13 +6550,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="5">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C13" s="5">
         <v>17</v>
       </c>
       <c r="D13" s="5">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E13" s="5">
         <v>2</v>
@@ -6565,7 +6565,7 @@
         <v>7</v>
       </c>
       <c r="G13" s="5">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H13" s="5">
         <v>2</v>
@@ -6726,13 +6726,13 @@
         <v>31</v>
       </c>
       <c r="B17" s="5">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C17" s="5">
         <v>14</v>
       </c>
       <c r="D17" s="5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E17" s="5">
         <v>2</v>
@@ -6741,7 +6741,7 @@
         <v>6</v>
       </c>
       <c r="G17" s="5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H17" s="5">
         <v>2</v>
@@ -6924,16 +6924,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.6409532567192602</v>
+        <v>0.5906859120759691</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.991267466172714</v>
+        <v>0.9937871277949679</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3416330937137799</v>
+        <v>0.334533576561465</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -6983,22 +6983,22 @@
         <v>8</v>
       </c>
       <c r="N4" s="4">
-        <v>1.766094359062572</v>
+        <v>1.115312996391822</v>
       </c>
       <c r="O4" s="5">
         <v>30</v>
       </c>
       <c r="P4" s="4">
-        <v>1.387741008144039</v>
+        <v>1.213511258802594</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.8840964060680003</v>
+        <v>0.3280788432423279</v>
       </c>
       <c r="R4" s="5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="S4" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -7042,16 +7042,16 @@
         <v>5</v>
       </c>
       <c r="N5" s="4">
-        <v>1.332918296894722</v>
+        <v>1.263115424559146</v>
       </c>
       <c r="O5" s="5">
         <v>31</v>
       </c>
       <c r="P5" s="4">
-        <v>1.453823721977243</v>
+        <v>1.46237796576412</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6626499254959582</v>
+        <v>0.6495862777206705</v>
       </c>
       <c r="R5" s="5">
         <v>28</v>
@@ -7224,13 +7224,13 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7546032606756954</v>
+        <v>0.7820458057085489</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6159488826781693</v>
+        <v>0.620036070236254</v>
       </c>
       <c r="Q3" s="4">
         <v>0.4872109944252669</v>
@@ -7283,16 +7283,16 @@
         <v>15</v>
       </c>
       <c r="N4" s="4">
-        <v>1.920016860514944</v>
+        <v>1.928914109348625</v>
       </c>
       <c r="O4" s="5">
         <v>33</v>
       </c>
       <c r="P4" s="4">
-        <v>0.691708900107349</v>
+        <v>0.6934126286074156</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3509700502193467</v>
+        <v>0.3507004366183262</v>
       </c>
       <c r="R4" s="5">
         <v>33</v>
@@ -7342,16 +7342,16 @@
         <v>5</v>
       </c>
       <c r="N5" s="4">
-        <v>1.189156844464183</v>
+        <v>1.275537508523485</v>
       </c>
       <c r="O5" s="5">
         <v>42</v>
       </c>
       <c r="P5" s="4">
-        <v>0.805013040795155</v>
+        <v>0.8064471639443078</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6048236732621839</v>
+        <v>0.5980402862322568</v>
       </c>
       <c r="R5" s="5">
         <v>41</v>
@@ -7524,22 +7524,22 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7627229089898466</v>
+        <v>0.4089060616111055</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8054292117150814</v>
+        <v>0.7236870114735463</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6164491271050745</v>
+        <v>0.4673374897218991</v>
       </c>
       <c r="R3" s="5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7583,22 +7583,22 @@
         <v>12</v>
       </c>
       <c r="N4" s="4">
-        <v>1.189337325845232</v>
+        <v>0.4131277917749685</v>
       </c>
       <c r="O4" s="5">
         <v>39</v>
       </c>
       <c r="P4" s="4">
-        <v>1.487755493928858</v>
+        <v>1.23058701249471</v>
       </c>
       <c r="Q4" s="4">
-        <v>1.032840754025461</v>
+        <v>0.3879555019000314</v>
       </c>
       <c r="R4" s="5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S4" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -7642,22 +7642,22 @@
         <v>11</v>
       </c>
       <c r="N5" s="4">
-        <v>1.22998805757707</v>
+        <v>0.6412674732519008</v>
       </c>
       <c r="O5" s="5">
         <v>43</v>
       </c>
       <c r="P5" s="4">
-        <v>1.469012977666904</v>
+        <v>1.298945182401227</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.895028218334031</v>
+        <v>0.4724286947912057</v>
       </c>
       <c r="R5" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S5" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -7824,16 +7824,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7586684513303984</v>
+        <v>0.6113502930816139</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6897172515029397</v>
+        <v>0.6536037656881374</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6064034814413113</v>
+        <v>0.5957624051288045</v>
       </c>
       <c r="R3" s="5">
         <v>36</v>
@@ -7883,16 +7883,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>0.9467560974037406</v>
+        <v>0.617370826397746</v>
       </c>
       <c r="O4" s="5">
         <v>25</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9802797807614826</v>
+        <v>0.8777860127576322</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5866795059409197</v>
+        <v>0.4813572785978977</v>
       </c>
       <c r="R4" s="5">
         <v>23</v>
@@ -7942,22 +7942,22 @@
         <v>7</v>
       </c>
       <c r="N5" s="4">
-        <v>1.079994520892309</v>
+        <v>0.8359448525407061</v>
       </c>
       <c r="O5" s="5">
         <v>41</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8897526150877952</v>
+        <v>0.8721583362271593</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6971208456280824</v>
+        <v>0.6195695022198228</v>
       </c>
       <c r="R5" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S5" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -8124,22 +8124,22 @@
         <v>11</v>
       </c>
       <c r="N3" s="4">
-        <v>0.954521056509479</v>
+        <v>0.1880811270689264</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>1.193898891272102</v>
+        <v>0.9621920875625194</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.8969963787681414</v>
+        <v>0.3012697666339965</v>
       </c>
       <c r="R3" s="5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="S3" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -8183,22 +8183,22 @@
         <v>11</v>
       </c>
       <c r="N4" s="4">
-        <v>1.102368709866022</v>
+        <v>0.3781587009589202</v>
       </c>
       <c r="O4" s="5">
         <v>42</v>
       </c>
       <c r="P4" s="4">
-        <v>1.335981947380894</v>
+        <v>1.068461378755022</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.8940850475884609</v>
+        <v>0.262865181818313</v>
       </c>
       <c r="R4" s="5">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="S4" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -8242,22 +8242,22 @@
         <v>11</v>
       </c>
       <c r="N5" s="4">
-        <v>1.136576230037624</v>
+        <v>0.275599745317777</v>
       </c>
       <c r="O5" s="5">
         <v>45</v>
       </c>
       <c r="P5" s="4">
-        <v>1.427722530399969</v>
+        <v>1.13148943596197</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.9701585029689158</v>
+        <v>0.3224148586434828</v>
       </c>
       <c r="R5" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S5" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
